--- a/Attemdance_test1.xlsx
+++ b/Attemdance_test1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codes\camcapsule-iot\CampusPulse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{476765AE-5618-482E-963F-EC6EAF88DEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EC5054-51BA-4F86-B8C2-269693137E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3151C842-3005-4B75-BCD9-D64DD0CB29DA}"/>
   </bookViews>
@@ -33,10 +33,10 @@
     <t>status</t>
   </si>
   <si>
-    <t>p</t>
+    <t>P</t>
   </si>
   <si>
-    <t>a</t>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -390,6 +390,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC0B546-7EA3-4C37-9614-26550EA30BAA}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
